--- a/multi_index/multi_index_est.xlsx
+++ b/multi_index/multi_index_est.xlsx
@@ -159,17 +159,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -194,6 +192,101 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -251,101 +344,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -640,6 +638,101 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -697,101 +790,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1143,99 +1141,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
@@ -1293,155 +1198,248 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
@@ -1544,25 +1542,25 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{3CB509FB-0A61-4DFF-88A2-0928134831A4}" name="Division" totalsRowLabel="Total" dataDxfId="51" totalsRowDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{B90B55CB-0AFD-4686-9302-C43D6DF4CE41}" name="Labor" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Currency"/>
-    <tableColumn id="2" xr3:uid="{A25A2163-1A44-47BB-9F6C-84AD2A735605}" name="Materials" totalsRowFunction="sum" dataDxfId="50" totalsRowDxfId="52" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{89CE31CC-0D30-4A0A-B77F-27CAA514A9A8}" name="Total" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="54" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{3CB509FB-0A61-4DFF-88A2-0928134831A4}" name="Division" totalsRowLabel="Total" dataDxfId="69" totalsRowDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{B90B55CB-0AFD-4686-9302-C43D6DF4CE41}" name="Labor" totalsRowFunction="sum" dataDxfId="67" totalsRowDxfId="66" dataCellStyle="Currency"/>
+    <tableColumn id="2" xr3:uid="{A25A2163-1A44-47BB-9F6C-84AD2A735605}" name="Materials" totalsRowFunction="sum" dataDxfId="65" totalsRowDxfId="64" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{89CE31CC-0D30-4A0A-B77F-27CAA514A9A8}" name="Total" totalsRowFunction="sum" dataDxfId="63" totalsRowDxfId="62" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(Table134[[#This Row],[Labor]:[Materials]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E824E2C2-90B8-4778-9DFA-3EFE3F3AEE54}" name="Duration" dataDxfId="55" totalsRowDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{13ADFD35-97A7-428D-8B8F-5815E339A031}" name="PPI_Index" dataDxfId="67" totalsRowDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{FA427198-5B8F-4304-8AF0-48FA5DC79016}" name="Mat_Index_Chng" dataDxfId="59" totalsRowDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{621D048F-E02E-4844-B3AD-C476AA3E26DF}" name="Mat_Inc" totalsRowFunction="sum" dataDxfId="57" totalsRowDxfId="56">
+    <tableColumn id="3" xr3:uid="{E824E2C2-90B8-4778-9DFA-3EFE3F3AEE54}" name="Duration" dataDxfId="61" totalsRowDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{13ADFD35-97A7-428D-8B8F-5815E339A031}" name="PPI_Index" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{FA427198-5B8F-4304-8AF0-48FA5DC79016}" name="Mat_Index_Chng" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="6" xr3:uid="{621D048F-E02E-4844-B3AD-C476AA3E26DF}" name="Mat_Inc" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="54">
       <calculatedColumnFormula>Table134[[#This Row],[Materials]]*((1+Table134[[#This Row],[Mat_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{7358118F-BDAB-4BD0-81D3-05A40BAD4B00}" name="Lab_Index_Chng" dataDxfId="58" totalsRowDxfId="64">
+    <tableColumn id="10" xr3:uid="{7358118F-BDAB-4BD0-81D3-05A40BAD4B00}" name="Lab_Index_Chng" dataDxfId="53" totalsRowDxfId="52">
       <calculatedColumnFormula>0.0373688251855644</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{57C12779-A238-4876-911C-7FA694BDE3FD}" name="Lab_Inc" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="63">
+    <tableColumn id="11" xr3:uid="{57C12779-A238-4876-911C-7FA694BDE3FD}" name="Lab_Inc" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50">
       <calculatedColumnFormula>Table134[[#This Row],[Labor]]*((1+Table134[[#This Row],[Lab_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{452E0C0D-4F77-4430-9CE5-23968F7FC924}" name="Escalated" totalsRowFunction="sum" dataDxfId="61" totalsRowDxfId="60" dataCellStyle="Currency">
+    <tableColumn id="7" xr3:uid="{452E0C0D-4F77-4430-9CE5-23968F7FC924}" name="Escalated" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(Table134[[#This Row],[Labor]],Table134[[#This Row],[Materials]],Table134[[#This Row],[Mat_Inc]],Table134[[#This Row],[Lab_Inc]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1586,25 +1584,25 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4D9369D3-EA65-4E15-AB31-ED1C59C59686}" name="Division" totalsRowLabel="Total" dataDxfId="44" totalsRowDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{EB4211A5-38B1-46AD-BEF9-8EAD09BDACF1}" name="Labor" totalsRowFunction="sum" dataDxfId="42" totalsRowDxfId="43" dataCellStyle="Currency"/>
-    <tableColumn id="2" xr3:uid="{C45A2B58-7BFE-4FC3-923B-105FDC460674}" name="Materials" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="41" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{E7AF7911-ECA9-47FE-8BA4-C5D111F21678}" name="Total" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="39" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{4D9369D3-EA65-4E15-AB31-ED1C59C59686}" name="Division" totalsRowLabel="Total" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{EB4211A5-38B1-46AD-BEF9-8EAD09BDACF1}" name="Labor" totalsRowFunction="sum" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Currency"/>
+    <tableColumn id="2" xr3:uid="{C45A2B58-7BFE-4FC3-923B-105FDC460674}" name="Materials" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{E7AF7911-ECA9-47FE-8BA4-C5D111F21678}" name="Total" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(Table1342[[#This Row],[Labor]:[Materials]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{78246E24-747E-46A2-901F-BF87F71C1A5A}" name="Duration" dataDxfId="36" totalsRowDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{245564A3-13A4-496A-A0FF-B16D2CAB0463}" name="PPI_Index" dataDxfId="34" totalsRowDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{458F9960-493C-47AB-B0FC-6B8D9CABF936}" name="Mat_Index_Chng" dataDxfId="32" totalsRowDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{6B213DF2-1D38-4968-9B5F-B9E482E08759}" name="Mat_Inc" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="31">
+    <tableColumn id="3" xr3:uid="{78246E24-747E-46A2-901F-BF87F71C1A5A}" name="Duration" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{245564A3-13A4-496A-A0FF-B16D2CAB0463}" name="PPI_Index" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{458F9960-493C-47AB-B0FC-6B8D9CABF936}" name="Mat_Index_Chng" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{6B213DF2-1D38-4968-9B5F-B9E482E08759}" name="Mat_Inc" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>Table1342[[#This Row],[Materials]]*((1+Table1342[[#This Row],[Mat_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{78080B15-5ED1-437D-BB1C-84906229A95B}" name="Lab_Index_Chng" dataDxfId="24" totalsRowDxfId="29">
+    <tableColumn id="10" xr3:uid="{78080B15-5ED1-437D-BB1C-84906229A95B}" name="Lab_Index_Chng" dataDxfId="29" totalsRowDxfId="28">
       <calculatedColumnFormula>0.260653188180404</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4A849DC8-6EE0-483B-B245-CF98F68747E0}" name="Lab_Inc" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="28">
+    <tableColumn id="11" xr3:uid="{4A849DC8-6EE0-483B-B245-CF98F68747E0}" name="Lab_Inc" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
       <calculatedColumnFormula>Table1342[[#This Row],[Labor]]*((1+Table1342[[#This Row],[Lab_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{91476317-BBB6-4FDC-92C0-9875995A1FD3}" name="Escalated" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="26" dataCellStyle="Currency">
+    <tableColumn id="7" xr3:uid="{91476317-BBB6-4FDC-92C0-9875995A1FD3}" name="Escalated" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(Table1342[[#This Row],[Labor]],Table1342[[#This Row],[Materials]],Table1342[[#This Row],[Mat_Inc]],Table1342[[#This Row],[Lab_Inc]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1628,25 +1626,25 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{14C1B3A5-CCE4-4FE1-AE0F-02F07A5EE734}" name="Division" totalsRowLabel="Total" dataDxfId="20" totalsRowDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{79585622-760A-4D22-A31E-B2236C990B71}" name="Labor" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="19" dataCellStyle="Currency"/>
-    <tableColumn id="2" xr3:uid="{0F8B79EC-94DE-40F3-ACA4-2A11764279B1}" name="Materials" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="17" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{ECCE32CC-8A0F-4ECD-B670-B15A86C0E880}" name="Total" totalsRowFunction="sum" dataDxfId="14" totalsRowDxfId="15" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{14C1B3A5-CCE4-4FE1-AE0F-02F07A5EE734}" name="Division" totalsRowLabel="Total" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{79585622-760A-4D22-A31E-B2236C990B71}" name="Labor" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Currency"/>
+    <tableColumn id="2" xr3:uid="{0F8B79EC-94DE-40F3-ACA4-2A11764279B1}" name="Materials" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{ECCE32CC-8A0F-4ECD-B670-B15A86C0E880}" name="Total" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(Table13423[[#This Row],[Labor]:[Materials]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8CF1D27E-4122-4117-87BD-7A5A2E225A56}" name="Duration" dataDxfId="12" totalsRowDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{166F56B5-ECDE-4AEB-ABA1-644F9A5479B4}" name="PPI_Index" dataDxfId="10" totalsRowDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{BC8A353D-5D00-4062-ACAE-B96044DB9399}" name="Mat_Index_Chng" dataDxfId="8" totalsRowDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{F6DD9706-27B2-4CC4-855F-BD9DA9DDA78A}" name="Mat_Inc" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
+    <tableColumn id="3" xr3:uid="{8CF1D27E-4122-4117-87BD-7A5A2E225A56}" name="Duration" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{166F56B5-ECDE-4AEB-ABA1-644F9A5479B4}" name="PPI_Index" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{BC8A353D-5D00-4062-ACAE-B96044DB9399}" name="Mat_Index_Chng" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{F6DD9706-27B2-4CC4-855F-BD9DA9DDA78A}" name="Mat_Inc" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>Table13423[[#This Row],[Materials]]*((1+Table13423[[#This Row],[Mat_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{AF8B2194-95CB-4046-88B4-F1466B39AEF8}" name="Lab_Index_Chng" dataDxfId="0" totalsRowDxfId="5">
+    <tableColumn id="10" xr3:uid="{AF8B2194-95CB-4046-88B4-F1466B39AEF8}" name="Lab_Index_Chng" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>0.46529284164859</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6D3A8FF6-630A-4FBA-8F46-306D6F8161C7}" name="Lab_Inc" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="4">
+    <tableColumn id="11" xr3:uid="{6D3A8FF6-630A-4FBA-8F46-306D6F8161C7}" name="Lab_Inc" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>Table13423[[#This Row],[Labor]]*((1+Table13423[[#This Row],[Lab_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A26F1002-B6A3-4FB5-BC55-2B8550DC4E4F}" name="Escalated" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="2" dataCellStyle="Currency">
+    <tableColumn id="7" xr3:uid="{A26F1002-B6A3-4FB5-BC55-2B8550DC4E4F}" name="Escalated" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Currency">
       <calculatedColumnFormula>SUM(Table13423[[#This Row],[Labor]],Table13423[[#This Row],[Materials]],Table13423[[#This Row],[Mat_Inc]],Table13423[[#This Row],[Lab_Inc]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1860,19 +1858,19 @@
   <cols>
     <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.06640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.59765625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F1">
@@ -1886,10 +1884,10 @@
       <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1910,7 +1908,7 @@
       <c r="K3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1918,13 +1916,13 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>125000</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>87500</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <f>SUM(Table134[[#This Row],[Labor]:[Materials]])</f>
         <v>212500</v>
       </c>
@@ -1949,7 +1947,7 @@
         <f>Table134[[#This Row],[Labor]]*((1+Table134[[#This Row],[Lab_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>377.49556082256055</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="6">
         <f>SUM(Table134[[#This Row],[Labor]],Table134[[#This Row],[Materials]],Table134[[#This Row],[Mat_Inc]],Table134[[#This Row],[Lab_Inc]])</f>
         <v>212875.63001568906</v>
       </c>
@@ -1958,13 +1956,13 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>97500</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>68250</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="6">
         <f>SUM(Table134[[#This Row],[Labor]:[Materials]])</f>
         <v>165750</v>
       </c>
@@ -1981,7 +1979,7 @@
         <f>Table134[[#This Row],[Materials]]*((1+Table134[[#This Row],[Mat_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>2131.3541753224818</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="1">
         <f t="shared" si="0"/>
         <v>3.7368825185564399E-2</v>
       </c>
@@ -1989,7 +1987,7 @@
         <f>Table134[[#This Row],[Labor]]*((1+Table134[[#This Row],[Lab_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>589.78229296945847</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="6">
         <f>SUM(Table134[[#This Row],[Labor]],Table134[[#This Row],[Materials]],Table134[[#This Row],[Mat_Inc]],Table134[[#This Row],[Lab_Inc]])</f>
         <v>168471.13646829195</v>
       </c>
@@ -1998,13 +1996,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>215000</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>105350</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <f>SUM(Table134[[#This Row],[Labor]:[Materials]])</f>
         <v>320350</v>
       </c>
@@ -2021,7 +2019,7 @@
         <f>Table134[[#This Row],[Materials]]*((1+Table134[[#This Row],[Mat_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>49.130235463076247</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="1">
         <f t="shared" si="0"/>
         <v>3.7368825185564399E-2</v>
       </c>
@@ -2029,7 +2027,7 @@
         <f>Table134[[#This Row],[Labor]]*((1+Table134[[#This Row],[Lab_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>1953.7655351588301</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="6">
         <f>SUM(Table134[[#This Row],[Labor]],Table134[[#This Row],[Materials]],Table134[[#This Row],[Mat_Inc]],Table134[[#This Row],[Lab_Inc]])</f>
         <v>322352.89577062189</v>
       </c>
@@ -2038,13 +2036,13 @@
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>192000</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>92160</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <f>SUM(Table134[[#This Row],[Labor]:[Materials]])</f>
         <v>284160</v>
       </c>
@@ -2061,7 +2059,7 @@
         <f>Table134[[#This Row],[Materials]]*((1+Table134[[#This Row],[Mat_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>-73.989788557231577</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="1">
         <f t="shared" si="0"/>
         <v>3.7368825185564399E-2</v>
       </c>
@@ -2069,7 +2067,7 @@
         <f>Table134[[#This Row],[Labor]]*((1+Table134[[#This Row],[Lab_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>2916.7296250382578</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="6">
         <f>SUM(Table134[[#This Row],[Labor]],Table134[[#This Row],[Materials]],Table134[[#This Row],[Mat_Inc]],Table134[[#This Row],[Lab_Inc]])</f>
         <v>287002.73983648105</v>
       </c>
@@ -2078,13 +2076,13 @@
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>34500</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>14835</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <f>SUM(Table134[[#This Row],[Labor]:[Materials]])</f>
         <v>49335</v>
       </c>
@@ -2101,7 +2099,7 @@
         <f>Table134[[#This Row],[Materials]]*((1+Table134[[#This Row],[Mat_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>661.68446769158845</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="1">
         <f t="shared" si="0"/>
         <v>3.7368825185564399E-2</v>
       </c>
@@ -2109,7 +2107,7 @@
         <f>Table134[[#This Row],[Labor]]*((1+Table134[[#This Row],[Lab_Index_Chng]])^(Table134[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>559.32160136137963</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="6">
         <f>SUM(Table134[[#This Row],[Labor]],Table134[[#This Row],[Materials]],Table134[[#This Row],[Mat_Inc]],Table134[[#This Row],[Lab_Inc]])</f>
         <v>50556.006069052964</v>
       </c>
@@ -2151,8 +2149,8 @@
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="7">
+      <c r="C11" s="8"/>
+      <c r="D11" s="2">
         <f>Table134[[#Totals],[Materials]]</f>
         <v>368095</v>
       </c>
@@ -2163,13 +2161,13 @@
       <c r="H11">
         <v>2.4277276966117499E-2</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="2">
         <f>D11*((1+H11)^(F11/F1)-1)</f>
         <v>3890.9273791802066</v>
       </c>
       <c r="J11" s="2"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
         <f>SUM(I11,D11)</f>
         <v>371985.92737918021</v>
       </c>
@@ -2191,11 +2189,11 @@
         <v>3.7368825185564399E-2</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="7">
+      <c r="K12" s="2">
         <f>C12*((1+H12)^(F12/F1)-1)</f>
         <v>10764.914298665393</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="2">
         <f>SUM(K12,C12)</f>
         <v>674764.91429866536</v>
       </c>
@@ -2204,13 +2202,13 @@
       <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="2">
         <f>SUM(L11:L12)</f>
         <v>1046750.8416778456</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L15" s="7">
+      <c r="L15" s="2">
         <f>L14-Table134[[#Totals],[Escalated]]</f>
         <v>5492.4335177086759</v>
       </c>
@@ -2233,19 +2231,19 @@
   <cols>
     <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.06640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.59765625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F1">
@@ -2259,10 +2257,10 @@
       <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -2283,7 +2281,7 @@
       <c r="K3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2291,13 +2289,13 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>125000</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>87500</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]:[Materials]])</f>
         <v>212500</v>
       </c>
@@ -2322,7 +2320,7 @@
         <f>Table1342[[#This Row],[Labor]]*((1+Table1342[[#This Row],[Lab_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>476.59765976570958</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]],Table1342[[#This Row],[Materials]],Table1342[[#This Row],[Mat_Inc]],Table1342[[#This Row],[Lab_Inc]])</f>
         <v>213421.03107196232</v>
       </c>
@@ -2331,13 +2329,13 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>97500</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>68250</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]:[Materials]])</f>
         <v>165750</v>
       </c>
@@ -2354,7 +2352,7 @@
         <f>Table1342[[#This Row],[Materials]]*((1+Table1342[[#This Row],[Mat_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>939.79650283786475</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="1">
         <f t="shared" si="0"/>
         <v>0.26065318818040401</v>
       </c>
@@ -2362,7 +2360,7 @@
         <f>Table1342[[#This Row],[Labor]]*((1+Table1342[[#This Row],[Lab_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>744.90973608931199</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]],Table1342[[#This Row],[Materials]],Table1342[[#This Row],[Mat_Inc]],Table1342[[#This Row],[Lab_Inc]])</f>
         <v>167434.70623892717</v>
       </c>
@@ -2371,13 +2369,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>215000</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>105350</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]:[Materials]])</f>
         <v>320350</v>
       </c>
@@ -2394,7 +2392,7 @@
         <f>Table1342[[#This Row],[Materials]]*((1+Table1342[[#This Row],[Mat_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>126.64624331955253</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="1">
         <f t="shared" si="0"/>
         <v>0.26065318818040401</v>
       </c>
@@ -2402,7 +2400,7 @@
         <f>Table1342[[#This Row],[Labor]]*((1+Table1342[[#This Row],[Lab_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>2468.6324005074212</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]],Table1342[[#This Row],[Materials]],Table1342[[#This Row],[Mat_Inc]],Table1342[[#This Row],[Lab_Inc]])</f>
         <v>322945.27864382695</v>
       </c>
@@ -2411,13 +2409,13 @@
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>192000</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>92160</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]:[Materials]])</f>
         <v>284160</v>
       </c>
@@ -2434,7 +2432,7 @@
         <f>Table1342[[#This Row],[Materials]]*((1+Table1342[[#This Row],[Mat_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>2781.6235111583296</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="1">
         <f t="shared" si="0"/>
         <v>0.26065318818040401</v>
       </c>
@@ -2442,7 +2440,7 @@
         <f>Table1342[[#This Row],[Labor]]*((1+Table1342[[#This Row],[Lab_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>3688.2882689936023</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]],Table1342[[#This Row],[Materials]],Table1342[[#This Row],[Mat_Inc]],Table1342[[#This Row],[Lab_Inc]])</f>
         <v>290629.91178015195</v>
       </c>
@@ -2451,13 +2449,13 @@
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>34500</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>14835</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]:[Materials]])</f>
         <v>49335</v>
       </c>
@@ -2474,7 +2472,7 @@
         <f>Table1342[[#This Row],[Materials]]*((1+Table1342[[#This Row],[Mat_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>467.77804375733456</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="1">
         <f t="shared" si="0"/>
         <v>0.26065318818040401</v>
       </c>
@@ -2482,7 +2480,7 @@
         <f>Table1342[[#This Row],[Labor]]*((1+Table1342[[#This Row],[Lab_Index_Chng]])^(Table1342[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>707.37189955142537</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="6">
         <f>SUM(Table1342[[#This Row],[Labor]],Table1342[[#This Row],[Materials]],Table1342[[#This Row],[Mat_Inc]],Table1342[[#This Row],[Lab_Inc]])</f>
         <v>50510.149943308759</v>
       </c>
@@ -2524,8 +2522,8 @@
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="7">
+      <c r="C11" s="8"/>
+      <c r="D11" s="2">
         <f>Table1342[[#Totals],[Materials]]</f>
         <v>368095</v>
       </c>
@@ -2536,13 +2534,13 @@
       <c r="H11">
         <v>0.28714843750000002</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="2">
         <f>D11*((1+H11)^(F11/F1)-1)</f>
         <v>8232.4798879479713</v>
       </c>
       <c r="J11" s="2"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
         <f>SUM(I11,D11)</f>
         <v>376327.47988794796</v>
       </c>
@@ -2564,11 +2562,11 @@
         <v>0.26065318818040401</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="7">
+      <c r="K12" s="2">
         <f>C12*((1+H12)^(F12/F1)-1)</f>
         <v>13614.346124699896</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="2">
         <f>SUM(K12,C12)</f>
         <v>677614.34612469992</v>
       </c>
@@ -2577,13 +2575,13 @@
       <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="2">
         <f>SUM(L11:L12)</f>
         <v>1053941.8260126479</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L15" s="7">
+      <c r="L15" s="2">
         <f>L14-Table1342[[#Totals],[Escalated]]</f>
         <v>9000.7483344707871</v>
       </c>
@@ -2606,19 +2604,19 @@
   <cols>
     <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.06640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.59765625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F1">
@@ -2632,10 +2630,10 @@
       <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -2656,7 +2654,7 @@
       <c r="K3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2664,13 +2662,13 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>125000</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>87500</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]:[Materials]])</f>
         <v>212500</v>
       </c>
@@ -2695,7 +2693,7 @@
         <f>Table13423[[#This Row],[Labor]]*((1+Table13423[[#This Row],[Lab_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>392.81594906717675</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]],Table13423[[#This Row],[Materials]],Table13423[[#This Row],[Mat_Inc]],Table13423[[#This Row],[Lab_Inc]])</f>
         <v>213217.1635411004</v>
       </c>
@@ -2704,13 +2702,13 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>97500</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>68250</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]:[Materials]])</f>
         <v>165750</v>
       </c>
@@ -2727,7 +2725,7 @@
         <f>Table13423[[#This Row],[Materials]]*((1+Table13423[[#This Row],[Mat_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>774.8918935492577</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="1">
         <f t="shared" si="0"/>
         <v>0.46529284164859003</v>
       </c>
@@ -2735,7 +2733,7 @@
         <f>Table13423[[#This Row],[Labor]]*((1+Table13423[[#This Row],[Lab_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>613.75573981260095</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]],Table13423[[#This Row],[Materials]],Table13423[[#This Row],[Mat_Inc]],Table13423[[#This Row],[Lab_Inc]])</f>
         <v>167138.64763336186</v>
       </c>
@@ -2744,13 +2742,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>215000</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>105350</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]:[Materials]])</f>
         <v>320350</v>
       </c>
@@ -2767,7 +2765,7 @@
         <f>Table13423[[#This Row],[Materials]]*((1+Table13423[[#This Row],[Mat_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>807.12256950291055</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="1">
         <f t="shared" si="0"/>
         <v>0.46529284164859003</v>
       </c>
@@ -2775,7 +2773,7 @@
         <f>Table13423[[#This Row],[Labor]]*((1+Table13423[[#This Row],[Lab_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>2033.3066538766409</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]],Table13423[[#This Row],[Materials]],Table13423[[#This Row],[Mat_Inc]],Table13423[[#This Row],[Lab_Inc]])</f>
         <v>323190.42922337953</v>
       </c>
@@ -2784,13 +2782,13 @@
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>192000</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>92160</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]:[Materials]])</f>
         <v>284160</v>
       </c>
@@ -2807,7 +2805,7 @@
         <f>Table13423[[#This Row],[Materials]]*((1+Table13423[[#This Row],[Mat_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>1943.1349429276838</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="1">
         <f t="shared" si="0"/>
         <v>0.46529284164859003</v>
       </c>
@@ -2815,7 +2813,7 @@
         <f>Table13423[[#This Row],[Labor]]*((1+Table13423[[#This Row],[Lab_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>3035.847088702255</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]],Table13423[[#This Row],[Materials]],Table13423[[#This Row],[Mat_Inc]],Table13423[[#This Row],[Lab_Inc]])</f>
         <v>289138.98203162994</v>
       </c>
@@ -2824,13 +2822,13 @@
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>34500</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>14835</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]:[Materials]])</f>
         <v>49335</v>
       </c>
@@ -2847,7 +2845,7 @@
         <f>Table13423[[#This Row],[Materials]]*((1+Table13423[[#This Row],[Mat_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>332.16827712787619</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="1">
         <f t="shared" si="0"/>
         <v>0.46529284164859003</v>
       </c>
@@ -2855,7 +2853,7 @@
         <f>Table13423[[#This Row],[Labor]]*((1+Table13423[[#This Row],[Lab_Index_Chng]])^(Table13423[[#This Row],[Duration]]/$F$1)-1)</f>
         <v>582.17587370784804</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="6">
         <f>SUM(Table13423[[#This Row],[Labor]],Table13423[[#This Row],[Materials]],Table13423[[#This Row],[Mat_Inc]],Table13423[[#This Row],[Lab_Inc]])</f>
         <v>50249.344150835728</v>
       </c>
@@ -2897,8 +2895,8 @@
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="7">
+      <c r="C11" s="8"/>
+      <c r="D11" s="2">
         <f>Table13423[[#Totals],[Materials]]</f>
         <v>368095</v>
       </c>
@@ -2909,13 +2907,13 @@
       <c r="H11">
         <v>0.443636363636364</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="2">
         <f>D11*((1+H11)^(F11/F1)-1)</f>
         <v>5967.4459765849597</v>
       </c>
       <c r="J11" s="2"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
         <f>SUM(I11,D11)</f>
         <v>374062.44597658498</v>
       </c>
@@ -2937,11 +2935,11 @@
         <v>0.46529284164859003</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="7">
+      <c r="K12" s="2">
         <f>C12*((1+H12)^(F12/F1)-1)</f>
         <v>11204.776236000322</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="2">
         <f>SUM(K12,C12)</f>
         <v>675204.77623600035</v>
       </c>
@@ -2950,13 +2948,13 @@
       <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="2">
         <f>SUM(L11:L12)</f>
         <v>1049267.2222125854</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L15" s="7">
+      <c r="L15" s="2">
         <f>L14-Table13423[[#Totals],[Escalated]]</f>
         <v>6332.6556322778342</v>
       </c>
